--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -7,14 +7,14 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="ИВО ИВАНОВ ЧЗС" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,6 +61,12 @@
     <t>2026-05-01</t>
   </si>
   <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>1156 Добрич бул. Добруджа</t>
+  </si>
+  <si>
     <t>TX4449TM</t>
   </si>
   <si>
@@ -67,7 +76,19 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>19:41</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>19:41:00</t>
+  </si>
+  <si>
+    <t>09:07:00</t>
+  </si>
+  <si>
+    <t>3231302640 3231302640</t>
+  </si>
+  <si>
+    <t>3232256602 3232256602</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВО ИВАНОВ ЧЗС</t>
@@ -491,24 +512,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.7109375" customWidth="1"/>
     <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -548,119 +571,169 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1156</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>50.04</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>72.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.52</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>76.06</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="L2">
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>45.8</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3">
+        <v>1.5</v>
+      </c>
+      <c r="I3" s="1">
+        <v>68.7</v>
+      </c>
+      <c r="J3">
+        <v>1.57</v>
+      </c>
+      <c r="K3" s="1">
+        <v>71.91</v>
+      </c>
+      <c r="L3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>78085</v>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
+    <row r="6" spans="1:14">
+      <c r="A6" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
     </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:14">
+      <c r="A7" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>9</v>
+      <c r="B8" s="6">
+        <v>95.84</v>
+      </c>
+      <c r="C8" s="6">
+        <v>2</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1.4687</v>
+      </c>
+      <c r="E8" s="6">
+        <v>140.76</v>
+      </c>
+      <c r="F8" s="6">
+        <v>147.97</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="6">
-        <v>50.04</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1.44</v>
-      </c>
-      <c r="E7" s="6">
-        <v>72.06</v>
-      </c>
-      <c r="F7" s="6">
-        <v>76.06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="9">
-        <v>50.04</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9">
-        <v>72.06</v>
-      </c>
-      <c r="F8" s="9">
-        <v>76.06</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="9">
+        <v>95.84</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2</v>
+      </c>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9">
+        <v>140.76</v>
+      </c>
+      <c r="F9" s="9">
+        <v>147.97</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -142,7 +142,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -152,12 +152,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -207,17 +201,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,10 +55,13 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-07</t>
   </si>
   <si>
-    <t>Добрич Добруджа</t>
+    <t>1156 Добрич бул. Добруджа</t>
   </si>
   <si>
     <t>TX4449TM</t>
@@ -67,7 +73,13 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-07 06:44:24</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>06:44:00</t>
+  </si>
+  <si>
+    <t>3234439365 3234439365</t>
   </si>
   <si>
     <t>Общи литри по продукт / ИВО ИВАНОВ ЧЗС</t>
@@ -485,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -494,15 +506,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -539,48 +553,60 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F2">
         <v>49.87</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
         <v>1.4</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>69.81999999999999</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.5</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>74.8</v>
       </c>
-      <c r="K2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
+      <c r="N2" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -588,29 +614,29 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6">
         <v>49.87</v>
@@ -628,9 +654,9 @@
         <v>74.8</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9">
         <v>49.87</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -106,7 +106,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -645,7 +645,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>1.4</v>
+        <v>1.40004</v>
       </c>
       <c r="E7" s="6">
         <v>69.81999999999999</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -497,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -510,13 +513,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,54 +562,60 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>49.87</v>
+        <v>49.867</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
-        <v>1.4</v>
+        <v>1.359</v>
       </c>
       <c r="I2" s="1">
-        <v>69.81999999999999</v>
+        <v>1.399</v>
       </c>
       <c r="J2">
+        <v>69.76393299999999</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
-        <v>74.8</v>
-      </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="1">
+        <v>74.8005</v>
+      </c>
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>21</v>
+      <c r="O2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -614,59 +623,59 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="6">
-        <v>49.87</v>
+        <v>49.867</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
       </c>
       <c r="D7" s="7">
-        <v>1.40004</v>
+        <v>1.399</v>
       </c>
       <c r="E7" s="6">
-        <v>69.81999999999999</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="F7" s="6">
         <v>74.8</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="9">
-        <v>49.87</v>
+        <v>49.867</v>
       </c>
       <c r="C8" s="9">
         <v>1</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="9">
-        <v>69.81999999999999</v>
+        <v>69.76000000000001</v>
       </c>
       <c r="F8" s="9">
         <v>74.8</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ИВО ИВАНОВ ЧЗС/ИВО ИВАНОВ ЧЗС.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="28">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -108,8 +105,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -202,10 +199,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -500,7 +497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -513,13 +510,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -562,60 +559,54 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>15</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>49.867</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>69.764</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>74.8</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.359</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.399</v>
-      </c>
-      <c r="J2">
-        <v>69.76393299999999</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>74.8005</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
         <v>21</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="3" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -623,49 +614,49 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:14">
       <c r="A6" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="C6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>27</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" s="6">
         <v>49.867</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="7">
         <v>1.399</v>
       </c>
-      <c r="E7" s="6">
-        <v>69.76000000000001</v>
-      </c>
-      <c r="F7" s="6">
+      <c r="E7" s="7">
+        <v>69.764</v>
+      </c>
+      <c r="F7" s="7">
         <v>74.8</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="9">
         <v>49.867</v>
@@ -675,7 +666,7 @@
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="9">
-        <v>69.76000000000001</v>
+        <v>69.764</v>
       </c>
       <c r="F8" s="9">
         <v>74.8</v>
